--- a/docs/d/86/inyear.xlsx
+++ b/docs/d/86/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 27 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 26 clubs short</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4696,8 +4696,8 @@
       <c r="Y39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z39" s="9" t="n">
-        <v>0</v>
+      <c r="Z39" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA39" s="10" t="n">
         <v>1</v>
@@ -6460,7 +6460,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6518,8 +6518,8 @@
       <c r="U57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V57" s="9" t="n">
-        <v>2</v>
+      <c r="V57" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>0</v>
@@ -11102,7 +11102,7 @@
         </is>
       </c>
       <c r="P102" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q102" s="9" t="n">
         <v>0</v>
@@ -11527,7 +11527,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -11659,7 +11659,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>

--- a/docs/d/86/inyear.xlsx
+++ b/docs/d/86/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,11 @@
       <c r="AB6" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC6" s="4" t="inlineStr"/>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1437,7 +1441,11 @@
       <c r="AB7" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC7" s="4" t="inlineStr"/>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1643,7 +1651,11 @@
       <c r="AB9" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC9" s="4" t="inlineStr"/>
+      <c r="AC9" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1845,7 +1857,11 @@
       <c r="AB11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC11" s="4" t="inlineStr"/>
+      <c r="AC11" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1946,7 +1962,11 @@
       <c r="AB12" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC12" s="4" t="inlineStr"/>
+      <c r="AC12" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -3691,7 +3711,11 @@
       <c r="AB29" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC29" s="4" t="inlineStr"/>
+      <c r="AC29" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -3792,7 +3816,11 @@
       <c r="AB30" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC30" s="4" t="inlineStr"/>
+      <c r="AC30" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -4095,7 +4123,11 @@
       <c r="AB33" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC33" s="4" t="inlineStr"/>
+      <c r="AC33" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -5214,7 +5246,11 @@
       <c r="AB44" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC44" s="4" t="inlineStr"/>
+      <c r="AC44" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -5416,7 +5452,11 @@
       <c r="AB46" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC46" s="4" t="inlineStr"/>
+      <c r="AC46" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -5517,7 +5557,11 @@
       <c r="AB47" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC47" s="4" t="inlineStr"/>
+      <c r="AC47" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -5921,7 +5965,11 @@
       <c r="AB51" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC51" s="4" t="inlineStr"/>
+      <c r="AC51" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -6022,7 +6070,11 @@
       <c r="AB52" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC52" s="4" t="inlineStr"/>
+      <c r="AC52" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -6745,7 +6797,11 @@
       <c r="AB59" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC59" s="4" t="inlineStr"/>
+      <c r="AC59" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -6846,7 +6902,11 @@
       <c r="AB60" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC60" s="4" t="inlineStr"/>
+      <c r="AC60" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -6947,7 +7007,11 @@
       <c r="AB61" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC61" s="4" t="inlineStr"/>
+      <c r="AC61" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -9710,7 +9774,11 @@
       <c r="AB88" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC88" s="4" t="inlineStr"/>
+      <c r="AC88" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -9811,7 +9879,11 @@
       <c r="AB89" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC89" s="4" t="inlineStr"/>
+      <c r="AC89" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -11140,7 +11212,11 @@
       <c r="AB102" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC102" s="4" t="inlineStr"/>
+      <c r="AC102" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AC102"/>

--- a/docs/d/86/inyear.xlsx
+++ b/docs/d/86/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 26 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 21 clubs short</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1717,8 +1717,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P10" s="9" t="n">
-        <v>3</v>
+      <c r="P10" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q10" s="9" t="n">
         <v>0</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2361,8 +2361,8 @@
       <c r="Y16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z16" s="9" t="n">
-        <v>0</v>
+      <c r="Z16" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA16" s="10" t="n">
         <v>1</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="P35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q35" s="9" t="n">
         <v>0</v>
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4526,8 +4526,8 @@
       <c r="Y37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" s="9" t="n">
-        <v>0</v>
+      <c r="Z37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA37" s="10" t="n">
         <v>1</v>
@@ -5414,7 +5414,7 @@
         </is>
       </c>
       <c r="P46" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q46" s="10" t="n">
         <v>2</v>
@@ -5429,7 +5429,7 @@
         <v>1</v>
       </c>
       <c r="U46" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V46" s="10" t="n">
         <v>4</v>
@@ -6096,7 +6096,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6166,8 +6166,8 @@
       <c r="Y53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z53" s="9" t="n">
-        <v>0</v>
+      <c r="Z53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA53" s="10" t="n">
         <v>1</v>
@@ -6526,13 +6526,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>4</v>
       </c>
       <c r="W57" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X57" s="10" t="n">
         <v>7</v>
@@ -7390,7 +7390,7 @@
         <v>0</v>
       </c>
       <c r="S65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T65" s="9" t="n">
         <v>0</v>
@@ -8309,7 +8309,7 @@
         <v>1</v>
       </c>
       <c r="Q74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74" s="9" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8646,8 +8646,8 @@
       <c r="Y77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z77" s="9" t="n">
-        <v>0</v>
+      <c r="Z77" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA77" s="10" t="n">
         <v>1</v>
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="P83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q83" s="9" t="n">
         <v>0</v>
@@ -9695,7 +9695,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9735,8 +9735,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P88" s="9" t="n">
-        <v>3</v>
+      <c r="P88" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q88" s="9" t="n">
         <v>1</v>
@@ -10725,7 +10725,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10795,8 +10795,8 @@
       <c r="Y98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" s="9" t="n">
-        <v>0</v>
+      <c r="Z98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA98" s="10" t="n">
         <v>1</v>
@@ -11177,7 +11177,7 @@
         <v>2</v>
       </c>
       <c r="Q102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R102" s="9" t="n">
         <v>0</v>
@@ -11372,7 +11372,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -11405,7 +11405,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -11570,7 +11570,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -11702,7 +11702,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -11900,7 +11900,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -11999,7 +11999,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -12065,7 +12065,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>

--- a/docs/d/86/inyear.xlsx
+++ b/docs/d/86/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 21 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 4 clubs short</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1222,8 +1222,8 @@
       <c r="Y5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="9" t="n">
-        <v>0</v>
+      <c r="Z5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA5" s="10" t="n">
         <v>1</v>
@@ -1298,16 +1298,16 @@
         </is>
       </c>
       <c r="P6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" s="9" t="n">
         <v>0</v>
@@ -1418,7 +1418,7 @@
         <v>1</v>
       </c>
       <c r="U7" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V7" s="10" t="n">
         <v>4</v>
@@ -1586,13 +1586,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -2058,8 +2058,8 @@
       <c r="Y13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z13" s="9" t="n">
-        <v>0</v>
+      <c r="Z13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA13" s="10" t="n">
         <v>1</v>
@@ -2804,7 +2804,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2874,8 +2874,8 @@
       <c r="Y21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z21" s="9" t="n">
-        <v>0</v>
+      <c r="Z21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA21" s="10" t="n">
         <v>1</v>
@@ -3476,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="S27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" s="10" t="n">
         <v>1</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -4013,8 +4013,8 @@
       <c r="Y32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z32" s="9" t="n">
-        <v>0</v>
+      <c r="Z32" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA32" s="10" t="n">
         <v>1</v>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4199,7 +4199,7 @@
         <v>0</v>
       </c>
       <c r="S34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T34" s="9" t="n">
         <v>0</v>
@@ -4219,8 +4219,8 @@
       <c r="Y34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z34" s="9" t="n">
-        <v>0</v>
+      <c r="Z34" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA34" s="10" t="n">
         <v>1</v>
@@ -5066,7 +5066,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -5136,8 +5136,8 @@
       <c r="Y43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z43" s="9" t="n">
-        <v>0</v>
+      <c r="Z43" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA43" s="10" t="n">
         <v>1</v>
@@ -5429,7 +5429,7 @@
         <v>1</v>
       </c>
       <c r="U46" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V46" s="10" t="n">
         <v>4</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5653,8 +5653,8 @@
       <c r="Y48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z48" s="9" t="n">
-        <v>0</v>
+      <c r="Z48" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA48" s="10" t="n">
         <v>1</v>
@@ -5829,7 +5829,7 @@
         <v>0</v>
       </c>
       <c r="Q50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R50" s="9" t="n">
         <v>0</v>
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="P56" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q56" s="10" t="n">
         <v>2</v>
@@ -6864,7 +6864,7 @@
         </is>
       </c>
       <c r="P60" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q60" s="10" t="n">
         <v>2</v>
@@ -6942,13 +6942,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
@@ -7175,7 +7175,7 @@
         </is>
       </c>
       <c r="P63" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q63" s="9" t="n">
         <v>0</v>
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7291,8 +7291,8 @@
       <c r="S64" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T64" s="9" t="n">
-        <v>0</v>
+      <c r="T64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U64" s="9" t="n">
         <v>0</v>
@@ -7309,8 +7309,8 @@
       <c r="Y64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z64" s="9" t="n">
-        <v>0</v>
+      <c r="Z64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA64" s="10" t="n">
         <v>1</v>
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7410,8 +7410,8 @@
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="9" t="n">
-        <v>0</v>
+      <c r="Z65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA65" s="10" t="n">
         <v>1</v>
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="P70" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R70" s="9" t="n">
         <v>0</v>
@@ -8160,7 +8160,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="P73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q73" s="9" t="n">
         <v>0</v>
@@ -8212,8 +8212,8 @@
       <c r="S73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T73" s="9" t="n">
-        <v>0</v>
+      <c r="T73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U73" s="9" t="n">
         <v>0</v>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8440,8 +8440,8 @@
       <c r="Y75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z75" s="9" t="n">
-        <v>0</v>
+      <c r="Z75" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA75" s="10" t="n">
         <v>1</v>
@@ -8681,7 +8681,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8751,8 +8751,8 @@
       <c r="Y78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z78" s="9" t="n">
-        <v>0</v>
+      <c r="Z78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA78" s="10" t="n">
         <v>1</v>
@@ -8883,7 +8883,7 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8953,8 +8953,8 @@
       <c r="Y80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z80" s="9" t="n">
-        <v>0</v>
+      <c r="Z80" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA80" s="10" t="n">
         <v>1</v>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9128,8 +9128,8 @@
       <c r="P82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" s="9" t="n">
-        <v>1</v>
+      <c r="Q82" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R82" s="9" t="n">
         <v>0</v>
@@ -9190,7 +9190,7 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -9260,8 +9260,8 @@
       <c r="Y83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z83" s="9" t="n">
-        <v>0</v>
+      <c r="Z83" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA83" s="10" t="n">
         <v>1</v>
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9563,8 +9563,8 @@
       <c r="Y86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z86" s="9" t="n">
-        <v>0</v>
+      <c r="Z86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA86" s="10" t="n">
         <v>1</v>
@@ -9847,7 +9847,7 @@
         <v>2</v>
       </c>
       <c r="R89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S89" s="10" t="n">
         <v>3</v>
@@ -10216,7 +10216,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10286,8 +10286,8 @@
       <c r="Y93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z93" s="9" t="n">
-        <v>0</v>
+      <c r="Z93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA93" s="10" t="n">
         <v>1</v>
@@ -10422,7 +10422,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -10492,8 +10492,8 @@
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="9" t="n">
-        <v>0</v>
+      <c r="Z95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
@@ -10523,7 +10523,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10593,8 +10593,8 @@
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
@@ -11306,7 +11306,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -11372,7 +11372,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -11438,7 +11438,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -11537,7 +11537,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -11636,7 +11636,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -11669,7 +11669,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -11801,7 +11801,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -11867,7 +11867,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -11900,7 +11900,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -11933,7 +11933,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -11966,7 +11966,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -12032,7 +12032,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>

--- a/docs/d/86/inyear.xlsx
+++ b/docs/d/86/inyear.xlsx
@@ -103,8 +103,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 4 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 4 clubs short</t>
         </is>
       </c>
     </row>
@@ -855,20 +855,20 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M2" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N2" s="4" t="inlineStr">
@@ -876,7 +876,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O2" s="8" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -956,20 +956,20 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M3" s="7" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -977,7 +977,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1061,20 +1061,20 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M4" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -1082,7 +1082,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O4" s="8" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1090,8 +1090,8 @@
       <c r="P4" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q4" s="9" t="n">
-        <v>1</v>
+      <c r="Q4" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R4" s="9" t="n">
         <v>0</v>
@@ -1166,20 +1166,20 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M5" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -1187,7 +1187,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O5" s="8" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1271,20 +1271,20 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M6" s="7" t="n">
+      <c r="M6" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -1292,7 +1292,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1306,8 +1306,8 @@
       <c r="R6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S6" s="9" t="n">
-        <v>1</v>
+      <c r="S6" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T6" s="9" t="n">
         <v>0</v>
@@ -1315,11 +1315,11 @@
       <c r="U6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="9" t="n">
-        <v>3</v>
+      <c r="V6" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" s="10" t="n">
         <v>7</v>
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1376,20 +1376,20 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M7" s="7" t="n">
+      <c r="M7" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -1397,7 +1397,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1423,8 +1423,8 @@
       <c r="V7" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W7" s="9" t="n">
-        <v>3</v>
+      <c r="W7" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X7" s="10" t="n">
         <v>7</v>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1481,20 +1481,20 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M8" s="7" t="n">
+      <c r="M8" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -1502,7 +1502,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O8" s="8" t="inlineStr">
+      <c r="O8" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1528,8 +1528,8 @@
       <c r="V8" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W8" s="9" t="n">
-        <v>3</v>
+      <c r="W8" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X8" s="10" t="n">
         <v>7</v>
@@ -1586,20 +1586,20 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2</v>
+        <v>-15</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M9" s="7" t="n">
+      <c r="M9" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -1607,7 +1607,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="O9" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1691,20 +1691,20 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M10" s="7" t="n">
+      <c r="M10" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -1712,7 +1712,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O10" s="8" t="inlineStr">
+      <c r="O10" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1792,20 +1792,20 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4</v>
+        <v>-8</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M11" s="7" t="n">
+      <c r="M11" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1813,13 +1813,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O11" s="8" t="inlineStr">
+      <c r="O11" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q11" s="9" t="n">
         <v>1</v>
@@ -1828,7 +1828,7 @@
         <v>0</v>
       </c>
       <c r="S11" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T11" s="10" t="n">
         <v>1</v>
@@ -1897,20 +1897,20 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1</v>
+        <v>-16</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M12" s="7" t="n">
+      <c r="M12" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1918,7 +1918,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="O12" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1927,7 +1927,7 @@
         <v>1</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" s="9" t="n">
         <v>0</v>
@@ -2002,20 +2002,20 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M13" s="7" t="n">
+      <c r="M13" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -2023,7 +2023,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2103,20 +2103,20 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M14" s="7" t="n">
+      <c r="M14" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -2124,7 +2124,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2204,20 +2204,20 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M15" s="7" t="n">
+      <c r="M15" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -2225,7 +2225,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
+      <c r="O15" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2252,7 +2252,7 @@
         <v>4</v>
       </c>
       <c r="W15" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X15" s="10" t="n">
         <v>7</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2305,20 +2305,20 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M16" s="7" t="n">
+      <c r="M16" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -2326,7 +2326,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O16" s="8" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2346,11 +2346,11 @@
       <c r="T16" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U16" s="9" t="n">
-        <v>0</v>
+      <c r="U16" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" s="9" t="n">
         <v>0</v>
@@ -2406,20 +2406,20 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M17" s="7" t="n">
+      <c r="M17" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -2427,7 +2427,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
+      <c r="O17" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2451,7 +2451,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2507,20 +2507,20 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M18" s="7" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -2528,7 +2528,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O18" s="8" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2612,20 +2612,20 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M19" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M19" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -2633,7 +2633,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O19" s="8" t="inlineStr">
+      <c r="O19" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2717,20 +2717,20 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M20" s="7" t="n">
+      <c r="M20" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -2738,7 +2738,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O20" s="8" t="inlineStr">
+      <c r="O20" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2818,20 +2818,20 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M21" s="7" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M21" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2839,7 +2839,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O21" s="8" t="inlineStr">
+      <c r="O21" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2927,12 +2927,12 @@
       <c r="K22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="8" t="inlineStr">
+      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M22" s="7" t="n">
+      <c r="M22" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2940,7 +2940,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O22" s="8" t="inlineStr">
+      <c r="O22" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3024,20 +3024,20 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M23" s="7" t="n">
+      <c r="M23" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -3045,7 +3045,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O23" s="8" t="inlineStr">
+      <c r="O23" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3129,20 +3129,20 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M24" s="7" t="n">
+      <c r="M24" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -3150,7 +3150,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O24" s="8" t="inlineStr">
+      <c r="O24" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3234,20 +3234,20 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3</v>
+        <v>-10</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M25" s="7" t="n">
+      <c r="M25" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -3255,7 +3255,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O25" s="8" t="inlineStr">
+      <c r="O25" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3278,8 +3278,8 @@
       <c r="U25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="9" t="n">
-        <v>3</v>
+      <c r="V25" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
@@ -3339,20 +3339,20 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M26" s="7" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M26" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -3360,7 +3360,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O26" s="8" t="inlineStr">
+      <c r="O26" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3440,20 +3440,20 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>50</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M27" s="7" t="n">
+      <c r="M27" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -3461,13 +3461,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O27" s="8" t="inlineStr">
+      <c r="O27" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="9" t="n">
         <v>0</v>
@@ -3485,7 +3485,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3545,20 +3545,20 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M28" s="7" t="n">
+      <c r="M28" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -3566,7 +3566,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O28" s="8" t="inlineStr">
+      <c r="O28" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3583,14 +3583,14 @@
       <c r="S28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T28" s="9" t="n">
-        <v>0</v>
+      <c r="T28" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V28" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W28" s="9" t="n">
         <v>0</v>
@@ -3646,20 +3646,20 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M29" s="7" t="n">
+      <c r="M29" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -3667,7 +3667,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O29" s="8" t="inlineStr">
+      <c r="O29" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3694,7 +3694,7 @@
         <v>4</v>
       </c>
       <c r="W29" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X29" s="10" t="n">
         <v>6</v>
@@ -3751,20 +3751,20 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M30" s="7" t="n">
+      <c r="M30" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -3772,7 +3772,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O30" s="8" t="inlineStr">
+      <c r="O30" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3856,20 +3856,20 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M31" s="7" t="n">
+      <c r="M31" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3877,7 +3877,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O31" s="8" t="inlineStr">
+      <c r="O31" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3957,20 +3957,20 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M32" s="7" t="n">
+      <c r="M32" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -3978,7 +3978,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O32" s="8" t="inlineStr">
+      <c r="O32" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4002,7 +4002,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W32" s="9" t="n">
         <v>0</v>
@@ -4058,20 +4058,20 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M33" s="7" t="n">
+      <c r="M33" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -4079,7 +4079,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O33" s="8" t="inlineStr">
+      <c r="O33" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4103,7 +4103,7 @@
         <v>0</v>
       </c>
       <c r="V33" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>0</v>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4163,20 +4163,20 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M34" s="7" t="n">
+      <c r="M34" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -4184,7 +4184,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O34" s="8" t="inlineStr">
+      <c r="O34" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4198,8 +4198,8 @@
       <c r="R34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S34" s="9" t="n">
-        <v>1</v>
+      <c r="S34" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T34" s="9" t="n">
         <v>0</v>
@@ -4264,20 +4264,20 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M35" s="7" t="n">
+      <c r="M35" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -4285,7 +4285,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O35" s="8" t="inlineStr">
+      <c r="O35" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4309,7 +4309,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4369,20 +4369,20 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M36" s="7" t="n">
+        <v>-14</v>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M36" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -4390,7 +4390,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O36" s="8" t="inlineStr">
+      <c r="O36" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4470,20 +4470,20 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M37" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M37" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -4491,7 +4491,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O37" s="8" t="inlineStr">
+      <c r="O37" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4517,8 +4517,8 @@
       <c r="V37" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W37" s="9" t="n">
-        <v>0</v>
+      <c r="W37" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X37" s="9" t="n">
         <v>0</v>
@@ -4571,20 +4571,20 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M38" s="7" t="n">
+        <v>-14</v>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M38" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -4592,7 +4592,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O38" s="8" t="inlineStr">
+      <c r="O38" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4672,20 +4672,20 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="8" t="inlineStr">
+        <v>-7</v>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M39" s="7" t="n">
+      <c r="M39" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -4693,7 +4693,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O39" s="8" t="inlineStr">
+      <c r="O39" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4773,20 +4773,20 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M40" s="7" t="n">
+      <c r="M40" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -4794,7 +4794,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O40" s="8" t="inlineStr">
+      <c r="O40" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4874,20 +4874,20 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M41" s="7" t="n">
+        <v>-13</v>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M41" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -4895,7 +4895,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O41" s="8" t="inlineStr">
+      <c r="O41" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4987,12 +4987,12 @@
       <c r="K42" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="8" t="inlineStr">
+      <c r="L42" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M42" s="7" t="n">
+      <c r="M42" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -5000,7 +5000,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O42" s="8" t="inlineStr">
+      <c r="O42" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5080,20 +5080,20 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M43" s="7" t="n">
+        <v>-14</v>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M43" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -5101,7 +5101,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O43" s="8" t="inlineStr">
+      <c r="O43" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5181,20 +5181,20 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>2</v>
+        <v>-11</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M44" s="7" t="n">
+      <c r="M44" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -5202,7 +5202,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O44" s="8" t="inlineStr">
+      <c r="O44" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5225,8 +5225,8 @@
       <c r="U44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V44" s="9" t="n">
-        <v>2</v>
+      <c r="V44" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5286,20 +5286,20 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L45" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M45" s="7" t="n">
+      <c r="M45" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -5307,7 +5307,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O45" s="8" t="inlineStr">
+      <c r="O45" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5373,7 +5373,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5387,20 +5387,20 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>5</v>
+        <v>-8</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M46" s="7" t="n">
+      <c r="M46" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -5408,13 +5408,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O46" s="8" t="inlineStr">
+      <c r="O46" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P46" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q46" s="10" t="n">
         <v>2</v>
@@ -5429,13 +5429,13 @@
         <v>1</v>
       </c>
       <c r="U46" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V46" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W46" s="9" t="n">
-        <v>1</v>
+      <c r="W46" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X46" s="10" t="n">
         <v>7</v>
@@ -5478,7 +5478,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5492,20 +5492,20 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>4</v>
+        <v>-8</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M47" s="7" t="n">
+      <c r="M47" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -5513,7 +5513,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O47" s="8" t="inlineStr">
+      <c r="O47" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5524,8 +5524,8 @@
       <c r="Q47" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R47" s="9" t="n">
-        <v>1</v>
+      <c r="R47" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S47" s="9" t="n">
         <v>0</v>
@@ -5533,8 +5533,8 @@
       <c r="T47" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U47" s="9" t="n">
-        <v>0</v>
+      <c r="U47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V47" s="10" t="n">
         <v>4</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5605,12 +5605,12 @@
       <c r="K48" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L48" s="8" t="inlineStr">
+      <c r="L48" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M48" s="7" t="n">
+      <c r="M48" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -5618,7 +5618,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O48" s="8" t="inlineStr">
+      <c r="O48" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5641,11 +5641,11 @@
       <c r="U48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V48" s="9" t="n">
-        <v>2</v>
+      <c r="V48" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X48" s="10" t="n">
         <v>5</v>
@@ -5698,20 +5698,20 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M49" s="7" t="n">
+      <c r="M49" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -5719,7 +5719,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O49" s="8" t="inlineStr">
+      <c r="O49" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5799,20 +5799,20 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L50" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M50" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L50" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M50" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -5820,7 +5820,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O50" s="8" t="inlineStr">
+      <c r="O50" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5900,20 +5900,20 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M51" s="7" t="n">
+      <c r="M51" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -5921,7 +5921,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O51" s="8" t="inlineStr">
+      <c r="O51" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5948,7 +5948,7 @@
         <v>4</v>
       </c>
       <c r="W51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X51" s="10" t="n">
         <v>6</v>
@@ -6005,20 +6005,20 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M52" s="7" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M52" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -6026,7 +6026,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O52" s="8" t="inlineStr">
+      <c r="O52" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6110,20 +6110,20 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M53" s="7" t="n">
+      <c r="M53" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -6131,7 +6131,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O53" s="8" t="inlineStr">
+      <c r="O53" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6155,7 +6155,7 @@
         <v>0</v>
       </c>
       <c r="V53" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -6215,20 +6215,20 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M54" s="7" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M54" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -6236,7 +6236,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O54" s="8" t="inlineStr">
+      <c r="O54" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6320,20 +6320,20 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M55" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M55" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -6341,7 +6341,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O55" s="8" t="inlineStr">
+      <c r="O55" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6365,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="V55" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
@@ -6421,20 +6421,20 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L56" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M56" s="7" t="n">
+      <c r="M56" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N56" s="4" t="inlineStr">
@@ -6442,7 +6442,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O56" s="8" t="inlineStr">
+      <c r="O56" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6526,20 +6526,20 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M57" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M57" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -6547,7 +6547,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O57" s="8" t="inlineStr">
+      <c r="O57" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6556,7 +6556,7 @@
         <v>0</v>
       </c>
       <c r="Q57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R57" s="9" t="n">
         <v>0</v>
@@ -6631,20 +6631,20 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M58" s="7" t="n">
+      <c r="M58" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N58" s="4" t="inlineStr">
@@ -6652,7 +6652,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O58" s="8" t="inlineStr">
+      <c r="O58" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6676,7 +6676,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
@@ -6718,7 +6718,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6732,20 +6732,20 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M59" s="7" t="n">
+      <c r="M59" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -6753,13 +6753,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O59" s="8" t="inlineStr">
+      <c r="O59" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P59" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q59" s="10" t="n">
         <v>2</v>
@@ -6767,8 +6767,8 @@
       <c r="R59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S59" s="9" t="n">
-        <v>1</v>
+      <c r="S59" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T59" s="9" t="n">
         <v>0</v>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6837,20 +6837,20 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M60" s="7" t="n">
+      <c r="M60" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N60" s="4" t="inlineStr">
@@ -6858,13 +6858,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O60" s="8" t="inlineStr">
+      <c r="O60" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
-      <c r="P60" s="9" t="n">
-        <v>3</v>
+      <c r="P60" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q60" s="10" t="n">
         <v>2</v>
@@ -6881,8 +6881,8 @@
       <c r="U60" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="V60" s="9" t="n">
-        <v>3</v>
+      <c r="V60" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W60" s="9" t="n">
         <v>0</v>
@@ -6928,7 +6928,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6942,20 +6942,20 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M61" s="7" t="n">
+      <c r="M61" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -6963,13 +6963,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O61" s="8" t="inlineStr">
+      <c r="O61" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
-      <c r="P61" s="9" t="n">
-        <v>2</v>
+      <c r="P61" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q61" s="9" t="n">
         <v>1</v>
@@ -6986,8 +6986,8 @@
       <c r="U61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V61" s="9" t="n">
-        <v>3</v>
+      <c r="V61" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
@@ -7047,20 +7047,20 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="8" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M62" s="7" t="n">
+      <c r="M62" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N62" s="4" t="inlineStr">
@@ -7068,7 +7068,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O62" s="8" t="inlineStr">
+      <c r="O62" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7092,7 +7092,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -7148,20 +7148,20 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L63" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M63" s="7" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L63" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M63" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N63" s="4" t="inlineStr">
@@ -7169,7 +7169,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O63" s="8" t="inlineStr">
+      <c r="O63" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7253,20 +7253,20 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L64" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M64" s="7" t="n">
+      <c r="M64" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N64" s="4" t="inlineStr">
@@ -7274,7 +7274,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O64" s="8" t="inlineStr">
+      <c r="O64" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7354,20 +7354,20 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L65" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M65" s="7" t="n">
+      <c r="M65" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N65" s="4" t="inlineStr">
@@ -7375,7 +7375,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O65" s="8" t="inlineStr">
+      <c r="O65" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7455,20 +7455,20 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L66" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M66" s="7" t="n">
+      <c r="M66" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N66" s="4" t="inlineStr">
@@ -7476,7 +7476,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O66" s="8" t="inlineStr">
+      <c r="O66" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7556,20 +7556,20 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M67" s="7" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M67" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N67" s="4" t="inlineStr">
@@ -7577,7 +7577,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O67" s="8" t="inlineStr">
+      <c r="O67" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7586,7 +7586,7 @@
         <v>1</v>
       </c>
       <c r="Q67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R67" s="9" t="n">
         <v>0</v>
@@ -7661,20 +7661,20 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M68" s="7" t="n">
+      <c r="M68" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N68" s="4" t="inlineStr">
@@ -7682,7 +7682,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O68" s="8" t="inlineStr">
+      <c r="O68" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7766,20 +7766,20 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M69" s="7" t="n">
+      <c r="M69" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N69" s="4" t="inlineStr">
@@ -7787,7 +7787,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O69" s="8" t="inlineStr">
+      <c r="O69" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7867,20 +7867,20 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M70" s="7" t="n">
+      <c r="M70" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N70" s="4" t="inlineStr">
@@ -7888,7 +7888,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O70" s="8" t="inlineStr">
+      <c r="O70" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7903,7 +7903,7 @@
         <v>0</v>
       </c>
       <c r="S70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T70" s="9" t="n">
         <v>0</v>
@@ -7985,7 +7985,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M71" s="7" t="n">
+      <c r="M71" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N71" s="4" t="inlineStr">
@@ -7993,7 +7993,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O71" s="8" t="inlineStr">
+      <c r="O71" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8073,20 +8073,20 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="8" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M72" s="7" t="n">
+      <c r="M72" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N72" s="4" t="inlineStr">
@@ -8094,7 +8094,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O72" s="8" t="inlineStr">
+      <c r="O72" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8118,7 +8118,7 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -8174,20 +8174,20 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M73" s="7" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M73" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
@@ -8195,7 +8195,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O73" s="8" t="inlineStr">
+      <c r="O73" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8279,20 +8279,20 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L74" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M74" s="7" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M74" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N74" s="4" t="inlineStr">
@@ -8300,7 +8300,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O74" s="8" t="inlineStr">
+      <c r="O74" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8384,20 +8384,20 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L75" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M75" s="7" t="n">
+      <c r="M75" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N75" s="4" t="inlineStr">
@@ -8405,7 +8405,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O75" s="8" t="inlineStr">
+      <c r="O75" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8414,7 +8414,7 @@
         <v>0</v>
       </c>
       <c r="Q75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R75" s="9" t="n">
         <v>0</v>
@@ -8471,7 +8471,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8485,20 +8485,20 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M76" s="7" t="n">
+      <c r="M76" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N76" s="4" t="inlineStr">
@@ -8506,7 +8506,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O76" s="8" t="inlineStr">
+      <c r="O76" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8529,8 +8529,8 @@
       <c r="U76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V76" s="9" t="n">
-        <v>2</v>
+      <c r="V76" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8590,20 +8590,20 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L77" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M77" s="7" t="n">
+      <c r="M77" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N77" s="4" t="inlineStr">
@@ -8611,7 +8611,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O77" s="8" t="inlineStr">
+      <c r="O77" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8695,20 +8695,20 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L78" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M78" s="7" t="n">
+      <c r="M78" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N78" s="4" t="inlineStr">
@@ -8716,7 +8716,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O78" s="8" t="inlineStr">
+      <c r="O78" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8740,7 +8740,7 @@
         <v>0</v>
       </c>
       <c r="V78" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -8782,7 +8782,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8796,20 +8796,20 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M79" s="7" t="n">
+      <c r="M79" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N79" s="4" t="inlineStr">
@@ -8817,7 +8817,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O79" s="8" t="inlineStr">
+      <c r="O79" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8825,8 +8825,8 @@
       <c r="P79" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q79" s="9" t="n">
-        <v>1</v>
+      <c r="Q79" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R79" s="9" t="n">
         <v>0</v>
@@ -8897,20 +8897,20 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L80" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M80" s="7" t="n">
+      <c r="M80" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N80" s="4" t="inlineStr">
@@ -8918,7 +8918,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O80" s="8" t="inlineStr">
+      <c r="O80" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8998,20 +8998,20 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L81" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M81" s="7" t="n">
+      <c r="M81" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N81" s="4" t="inlineStr">
@@ -9019,7 +9019,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O81" s="8" t="inlineStr">
+      <c r="O81" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9043,7 +9043,7 @@
         <v>0</v>
       </c>
       <c r="V81" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W81" s="9" t="n">
         <v>0</v>
@@ -9099,20 +9099,20 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="8" t="inlineStr">
+        <v>-7</v>
+      </c>
+      <c r="L82" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M82" s="7" t="n">
+      <c r="M82" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N82" s="4" t="inlineStr">
@@ -9120,7 +9120,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O82" s="8" t="inlineStr">
+      <c r="O82" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9204,20 +9204,20 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L83" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M83" s="7" t="n">
+      <c r="M83" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N83" s="4" t="inlineStr">
@@ -9225,7 +9225,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O83" s="8" t="inlineStr">
+      <c r="O83" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9249,7 +9249,7 @@
         <v>0</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
@@ -9313,12 +9313,12 @@
       <c r="K84" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L84" s="8" t="inlineStr">
+      <c r="L84" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M84" s="7" t="n">
+      <c r="M84" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N84" s="4" t="inlineStr">
@@ -9326,7 +9326,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O84" s="8" t="inlineStr">
+      <c r="O84" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9406,20 +9406,20 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L85" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L85" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M85" s="7" t="n">
+      <c r="M85" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N85" s="4" t="inlineStr">
@@ -9427,7 +9427,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O85" s="8" t="inlineStr">
+      <c r="O85" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9507,20 +9507,20 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L86" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M86" s="7" t="n">
+      <c r="M86" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N86" s="4" t="inlineStr">
@@ -9528,7 +9528,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O86" s="8" t="inlineStr">
+      <c r="O86" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9608,20 +9608,20 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L87" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M87" s="7" t="n">
+      <c r="M87" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N87" s="4" t="inlineStr">
@@ -9629,7 +9629,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O87" s="8" t="inlineStr">
+      <c r="O87" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9695,7 +9695,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9709,20 +9709,20 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M88" s="7" t="n">
+      <c r="M88" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N88" s="4" t="inlineStr">
@@ -9730,7 +9730,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O88" s="8" t="inlineStr">
+      <c r="O88" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9738,11 +9738,11 @@
       <c r="P88" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q88" s="9" t="n">
-        <v>1</v>
+      <c r="Q88" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S88" s="9" t="n">
         <v>1</v>
@@ -9751,10 +9751,10 @@
         <v>1</v>
       </c>
       <c r="U88" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V88" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
@@ -9814,20 +9814,20 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M89" s="7" t="n">
+      <c r="M89" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N89" s="4" t="inlineStr">
@@ -9835,7 +9835,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O89" s="8" t="inlineStr">
+      <c r="O89" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9927,12 +9927,12 @@
       <c r="K90" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L90" s="8" t="inlineStr">
+      <c r="L90" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M90" s="7" t="n">
+      <c r="M90" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N90" s="4" t="inlineStr">
@@ -9940,7 +9940,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O90" s="8" t="inlineStr">
+      <c r="O90" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10006,7 +10006,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -10020,20 +10020,20 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L91" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M91" s="7" t="n">
+      <c r="M91" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N91" s="4" t="inlineStr">
@@ -10041,7 +10041,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O91" s="8" t="inlineStr">
+      <c r="O91" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10055,8 +10055,8 @@
       <c r="R91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S91" s="9" t="n">
-        <v>1</v>
+      <c r="S91" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T91" s="9" t="n">
         <v>0</v>
@@ -10065,7 +10065,7 @@
         <v>0</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
@@ -10111,7 +10111,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10125,20 +10125,20 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M92" s="7" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L92" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M92" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N92" s="4" t="inlineStr">
@@ -10146,7 +10146,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O92" s="8" t="inlineStr">
+      <c r="O92" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10163,8 +10163,8 @@
       <c r="S92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T92" s="9" t="n">
-        <v>0</v>
+      <c r="T92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U92" s="9" t="n">
         <v>0</v>
@@ -10230,20 +10230,20 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L93" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M93" s="7" t="n">
+      <c r="M93" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N93" s="4" t="inlineStr">
@@ -10251,7 +10251,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O93" s="8" t="inlineStr">
+      <c r="O93" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10331,20 +10331,20 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L94" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M94" s="7" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L94" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M94" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N94" s="4" t="inlineStr">
@@ -10352,7 +10352,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O94" s="8" t="inlineStr">
+      <c r="O94" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10436,20 +10436,20 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M95" s="7" t="n">
+      <c r="M95" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N95" s="4" t="inlineStr">
@@ -10457,7 +10457,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O95" s="8" t="inlineStr">
+      <c r="O95" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10537,20 +10537,20 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L96" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M96" s="7" t="n">
+      <c r="M96" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N96" s="4" t="inlineStr">
@@ -10558,7 +10558,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O96" s="8" t="inlineStr">
+      <c r="O96" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10638,20 +10638,20 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L97" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M97" s="7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M97" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N97" s="4" t="inlineStr">
@@ -10659,7 +10659,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O97" s="8" t="inlineStr">
+      <c r="O97" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10739,20 +10739,20 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L98" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M98" s="7" t="n">
+        <v>-14</v>
+      </c>
+      <c r="L98" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M98" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N98" s="4" t="inlineStr">
@@ -10760,7 +10760,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O98" s="8" t="inlineStr">
+      <c r="O98" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10787,7 +10787,7 @@
         <v>4</v>
       </c>
       <c r="W98" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X98" s="10" t="n">
         <v>5</v>
@@ -10840,20 +10840,20 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L99" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M99" s="7" t="n">
+      <c r="M99" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N99" s="4" t="inlineStr">
@@ -10861,7 +10861,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O99" s="8" t="inlineStr">
+      <c r="O99" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10941,20 +10941,20 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M100" s="7" t="n">
+      <c r="M100" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N100" s="4" t="inlineStr">
@@ -10962,7 +10962,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O100" s="8" t="inlineStr">
+      <c r="O100" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11046,20 +11046,20 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M101" s="7" t="n">
+      <c r="M101" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N101" s="4" t="inlineStr">
@@ -11067,7 +11067,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O101" s="8" t="inlineStr">
+      <c r="O101" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11091,7 +11091,7 @@
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -11133,7 +11133,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -11147,20 +11147,20 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M102" s="7" t="n">
+      <c r="M102" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N102" s="4" t="inlineStr">
@@ -11168,7 +11168,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O102" s="8" t="inlineStr">
+      <c r="O102" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11191,11 +11191,11 @@
       <c r="U102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V102" s="9" t="n">
-        <v>1</v>
+      <c r="V102" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X102" s="10" t="n">
         <v>7</v>
@@ -11306,7 +11306,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -11321,7 +11321,7 @@
         <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -11339,7 +11339,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>3.25</v>
+        <v>4.25</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -11405,7 +11405,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -11453,7 +11453,7 @@
         <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -11471,7 +11471,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -11486,7 +11486,7 @@
         <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -11504,7 +11504,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -11537,7 +11537,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -11570,7 +11570,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -11585,7 +11585,7 @@
         <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -11618,7 +11618,7 @@
         <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -11636,7 +11636,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -11651,7 +11651,7 @@
         <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -11669,13 +11669,13 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -11684,7 +11684,7 @@
         <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -11717,7 +11717,7 @@
         <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -11750,7 +11750,7 @@
         <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -11768,7 +11768,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -11816,7 +11816,7 @@
         <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -11849,7 +11849,7 @@
         <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -11882,7 +11882,7 @@
         <v>5</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -11900,7 +11900,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -11999,13 +11999,13 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -12014,7 +12014,7 @@
         <v>5</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -12047,7 +12047,7 @@
         <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -12065,7 +12065,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -12080,7 +12080,7 @@
         <v>6</v>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/86/inyear.xlsx
+++ b/docs/d/86/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/86/inyear.xlsx
+++ b/docs/d/86/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/86/inyear.xlsx
+++ b/docs/d/86/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/86/inyear.xlsx
+++ b/docs/d/86/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/86/inyear.xlsx
+++ b/docs/d/86/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 4 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 4 clubs short</t>
         </is>
       </c>
     </row>
@@ -1271,13 +1271,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>4</v>
       </c>
       <c r="W6" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X6" s="10" t="n">
         <v>7</v>
@@ -1481,13 +1481,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>4</v>
       </c>
       <c r="W8" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X8" s="10" t="n">
         <v>7</v>
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1624,8 +1624,8 @@
       <c r="S9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T9" s="9" t="n">
-        <v>0</v>
+      <c r="T9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U9" s="9" t="n">
         <v>0</v>
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1691,13 +1691,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -1735,8 +1735,8 @@
       <c r="U10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V10" s="9" t="n">
-        <v>2</v>
+      <c r="V10" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="P15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="9" t="n">
         <v>1</v>
@@ -2818,13 +2818,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>50</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-24</v>
+        <v>-23</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3545,13 +3545,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3589,8 +3589,8 @@
       <c r="U28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V28" s="9" t="n">
-        <v>3</v>
+      <c r="V28" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W28" s="9" t="n">
         <v>0</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -3995,8 +3995,8 @@
       <c r="S32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T32" s="9" t="n">
-        <v>0</v>
+      <c r="T32" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U32" s="9" t="n">
         <v>0</v>
@@ -4874,13 +4874,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5492,13 +5492,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>0</v>
       </c>
       <c r="S51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T51" s="9" t="n">
         <v>0</v>
@@ -6096,7 +6096,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6110,13 +6110,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         </is>
       </c>
       <c r="P53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q53" s="9" t="n">
         <v>1</v>
@@ -6148,8 +6148,8 @@
       <c r="S53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T53" s="9" t="n">
-        <v>0</v>
+      <c r="T53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U53" s="9" t="n">
         <v>0</v>
@@ -6512,7 +6512,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6555,8 +6555,8 @@
       <c r="P57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" s="9" t="n">
-        <v>1</v>
+      <c r="Q57" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R57" s="9" t="n">
         <v>0</v>
@@ -6631,13 +6631,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>2</v>
       </c>
       <c r="R60" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S60" s="10" t="n">
         <v>2</v>
@@ -6879,7 +6879,7 @@
         <v>1</v>
       </c>
       <c r="U60" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V60" s="10" t="n">
         <v>4</v>
@@ -6942,13 +6942,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>4</v>
       </c>
       <c r="W61" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X61" s="10" t="n">
         <v>7</v>
@@ -7354,13 +7354,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -8174,13 +8174,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -8279,13 +8279,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>-15</v>
+        <v>-13</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>0</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -8471,7 +8471,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8520,8 +8520,8 @@
       <c r="R76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S76" s="9" t="n">
-        <v>1</v>
+      <c r="S76" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T76" s="9" t="n">
         <v>0</v>
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>2</v>
       </c>
       <c r="R79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S79" s="9" t="n">
         <v>0</v>
@@ -8897,13 +8897,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>0</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="P85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q85" s="9" t="n">
         <v>0</v>
@@ -10331,13 +10331,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>-15</v>
+        <v>-13</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -10537,13 +10537,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10638,13 +10638,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10739,13 +10739,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -11372,7 +11372,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -11504,7 +11504,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -11537,7 +11537,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -11702,7 +11702,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -11735,7 +11735,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -11900,7 +11900,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>

--- a/docs/d/86/inyear.xlsx
+++ b/docs/d/86/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 4 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 4 clubs short</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1309,8 +1309,8 @@
       <c r="S6" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T6" s="9" t="n">
-        <v>0</v>
+      <c r="T6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U6" s="9" t="n">
         <v>0</v>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1481,13 +1481,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1507,8 +1507,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P8" s="9" t="n">
-        <v>2</v>
+      <c r="P8" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q8" s="10" t="n">
         <v>2</v>
@@ -1529,7 +1529,7 @@
         <v>4</v>
       </c>
       <c r="W8" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X8" s="10" t="n">
         <v>7</v>
@@ -1586,13 +1586,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="P10" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="9" t="n">
         <v>0</v>
@@ -1834,7 +1834,7 @@
         <v>1</v>
       </c>
       <c r="U11" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V11" s="10" t="n">
         <v>4</v>
@@ -2493,7 +2493,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2507,13 +2507,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2542,8 +2542,8 @@
       <c r="R18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S18" s="9" t="n">
-        <v>1</v>
+      <c r="S18" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="T18" s="9" t="n">
         <v>0</v>
@@ -2552,7 +2552,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W18" s="9" t="n">
         <v>0</v>
@@ -3234,13 +3234,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>4</v>
       </c>
       <c r="W25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25" s="10" t="n">
         <v>7</v>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="P26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="9" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
         <v>0</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" s="9" t="n">
         <v>0</v>
@@ -3751,13 +3751,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-17</v>
+        <v>-14</v>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W30" s="9" t="n">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
@@ -4163,13 +4163,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>0</v>
       </c>
       <c r="V34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>0</v>
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>4</v>
       </c>
       <c r="W44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X44" s="10" t="n">
         <v>7</v>
@@ -5373,7 +5373,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5419,8 +5419,8 @@
       <c r="Q46" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R46" s="9" t="n">
-        <v>1</v>
+      <c r="R46" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S46" s="10" t="n">
         <v>8</v>
@@ -5492,13 +5492,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -6215,17 +6215,17 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>-10</v>
-      </c>
-      <c r="L54" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-4</v>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M54" s="8" t="n">
@@ -6259,11 +6259,11 @@
       <c r="U54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V54" s="9" t="n">
-        <v>1</v>
+      <c r="V54" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W54" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X54" s="10" t="n">
         <v>6</v>
@@ -7148,13 +7148,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7354,13 +7354,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -7867,13 +7867,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>2</v>
       </c>
       <c r="R76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S76" s="10" t="n">
         <v>2</v>
@@ -9850,7 +9850,7 @@
         <v>1</v>
       </c>
       <c r="S89" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T89" s="10" t="n">
         <v>1</v>
@@ -9955,7 +9955,7 @@
         <v>0</v>
       </c>
       <c r="S90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T90" s="9" t="n">
         <v>0</v>
@@ -10331,17 +10331,17 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>-13</v>
-      </c>
-      <c r="L94" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-10</v>
+      </c>
+      <c r="L94" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M94" s="8" t="n">
@@ -10376,7 +10376,7 @@
         <v>0</v>
       </c>
       <c r="V94" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W94" s="9" t="n">
         <v>0</v>
@@ -10537,13 +10537,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>0</v>
       </c>
       <c r="Q98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R98" s="9" t="n">
         <v>0</v>
@@ -10840,13 +10840,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>0</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -10941,13 +10941,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -11438,7 +11438,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -11636,7 +11636,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -11702,7 +11702,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -11717,7 +11717,7 @@
         <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -12047,7 +12047,7 @@
         <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
